--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>48998</t>
   </si>
@@ -158,52 +158,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2D0B36A741C7BB87D58075C535C874D6</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>9BF5893F5DDACD5FBB15E7FEB382E4C6</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
     <t>Subdirección Jurídica.</t>
   </si>
   <si>
-    <t>12/01/2023</t>
+    <t>26/07/2023</t>
   </si>
   <si>
     <t>10/01/2023</t>
   </si>
   <si>
     <t>Del periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  organismos internacionales</t>
-  </si>
-  <si>
-    <t>40594911A6B9C6B5688992AB54B6EC65</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>ver nota</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  organismos internacionales</t>
   </si>
   <si>
     <t>Comité contra las Desapariciones Forzadas</t>
@@ -707,10 +686,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -939,43 +918,43 @@
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>51</v>
@@ -988,59 +967,6 @@
       </c>
       <c r="Q8" s="2" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +980,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I200">
       <formula1>Hidden_18</formula1>
     </dataValidation>
   </dataValidations>
@@ -1069,187 +995,187 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
